--- a/data_lake/datos_diarios_preliminares/dt=2026-07-31/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-31/Temp-max-julio-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE9E923-7937-4F1F-9ED1-193A8CBB80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC5DE1A-9496-422B-8746-B16D53F83329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9514,11 +9514,13 @@
       <c r="AG5" s="57">
         <v>31.3</v>
       </c>
-      <c r="AH5" s="57"/>
+      <c r="AH5" s="57">
+        <v>31.5</v>
+      </c>
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9536,11 +9538,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.048275862068969</v>
+        <v>31.063333333333336</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.85090408606074064</v>
+        <v>0.86596155732510738</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9643,11 +9645,13 @@
       <c r="AG6" s="57">
         <v>30.6</v>
       </c>
-      <c r="AH6" s="57"/>
+      <c r="AH6" s="57">
+        <v>30.9</v>
+      </c>
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9665,11 +9669,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.596551724137928</v>
+        <v>30.606666666666666</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-5.7728672884412191E-2</v>
+        <v>-4.7613730355674733E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9772,11 +9776,13 @@
       <c r="AG7" s="57">
         <v>35</v>
       </c>
-      <c r="AH7" s="57"/>
+      <c r="AH7" s="57">
+        <v>36.799999999999997</v>
+      </c>
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9794,11 +9800,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.348275862068959</v>
+        <v>35.396666666666661</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>1.9822598544998868</v>
+        <v>2.0306506590975886</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9901,11 +9907,13 @@
       <c r="AG8" s="57">
         <v>34.299999999999997</v>
       </c>
-      <c r="AH8" s="57"/>
+      <c r="AH8" s="57">
+        <v>34.4</v>
+      </c>
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>34.299999999999997</v>
+        <v>34.4</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9923,11 +9931,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.193103448275863</v>
+        <v>33.233333333333334</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>0.94406043752317004</v>
+        <v>0.98429032258064098</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10030,33 +10038,35 @@
       <c r="AG9" s="57">
         <v>34.9</v>
       </c>
-      <c r="AH9" s="57"/>
+      <c r="AH9" s="57">
+        <v>37.6</v>
+      </c>
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
-        <v>37.299999999999997</v>
+        <v>37.6</v>
       </c>
       <c r="AL9" s="22">
         <v>38.4</v>
       </c>
       <c r="AM9" s="23">
         <f t="shared" si="2"/>
-        <v>-1.1000000000000014</v>
+        <v>-0.79999999999999716</v>
       </c>
       <c r="AN9" s="23">
         <v>33.091246137683846</v>
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>33.944827586206891</v>
+        <v>34.066666666666663</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.85358144852304463</v>
+        <v>0.97542052898281639</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10159,11 +10169,13 @@
       <c r="AG10" s="57">
         <v>37.200000000000003</v>
       </c>
-      <c r="AH10" s="57"/>
+      <c r="AH10" s="57">
+        <v>37.299999999999997</v>
+      </c>
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>37.200000000000003</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -10181,11 +10193,11 @@
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.931034482758612</v>
+        <v>35.976666666666659</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.55079625509825547</v>
+        <v>0.59642843900630282</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10288,33 +10300,35 @@
       <c r="AG11" s="57">
         <v>39.799999999999997</v>
       </c>
-      <c r="AH11" s="57"/>
+      <c r="AH11" s="57">
+        <v>41.2</v>
+      </c>
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>39.799999999999997</v>
+        <v>41.2</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
-        <v>40.799999999999997</v>
+        <v>41.2</v>
       </c>
       <c r="AL11" s="22">
         <v>41.4</v>
       </c>
       <c r="AM11" s="23">
         <f t="shared" si="2"/>
-        <v>-0.60000000000000142</v>
+        <v>-0.19999999999999574</v>
       </c>
       <c r="AN11" s="23">
         <v>35.537284092848601</v>
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.193103448275849</v>
+        <v>38.293333333333322</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.6558193554272478</v>
+        <v>2.756049240484721</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10417,11 +10431,13 @@
       <c r="AG12" s="57">
         <v>35.200000000000003</v>
       </c>
-      <c r="AH12" s="57"/>
+      <c r="AH12" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>35.200000000000003</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10439,11 +10455,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.648275862068964</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.4596517158952267</v>
+        <v>2.5113758538262658</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10546,11 +10562,13 @@
       <c r="AG13" s="57">
         <v>35.6</v>
       </c>
-      <c r="AH13" s="57"/>
+      <c r="AH13" s="57">
+        <v>37.6</v>
+      </c>
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10568,11 +10586,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.310344827586206</v>
+        <v>35.386666666666663</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>1.9285527128908697</v>
+        <v>2.0048745519713265</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10675,11 +10693,13 @@
       <c r="AG14" s="57">
         <v>36.299999999999997</v>
       </c>
-      <c r="AH14" s="57"/>
+      <c r="AH14" s="57">
+        <v>36.6</v>
+      </c>
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>36.299999999999997</v>
+        <v>36.6</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10697,11 +10717,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>34.682758620689647</v>
+        <v>34.746666666666663</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.4578220214754154</v>
+        <v>1.521730067452431</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10804,11 +10824,13 @@
       <c r="AG15" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="AH15" s="57"/>
+      <c r="AH15" s="57">
+        <v>33.5</v>
+      </c>
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>33.5</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10826,11 +10848,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.848275862068963</v>
+        <v>31.903333333333329</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>0.11293840598901284</v>
+        <v>0.16799587725337872</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10982,11 +11004,13 @@
       <c r="AG17" s="57">
         <v>35.5</v>
       </c>
-      <c r="AH17" s="57"/>
+      <c r="AH17" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -11004,11 +11028,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.168965517241375</v>
+        <v>34.236666666666665</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.4949833147942186</v>
+        <v>1.5626844642195081</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11111,11 +11135,13 @@
       <c r="AG18" s="57">
         <v>28.7</v>
       </c>
-      <c r="AH18" s="57"/>
+      <c r="AH18" s="57">
+        <v>29.6</v>
+      </c>
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -11133,11 +11159,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.903448275862079</v>
+        <v>27.960000000000012</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.8435774219052092</v>
+        <v>1.9001291460431418</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11240,11 +11266,13 @@
       <c r="AG19" s="57">
         <v>36.799999999999997</v>
       </c>
-      <c r="AH19" s="57"/>
+      <c r="AH19" s="57">
+        <v>34.799999999999997</v>
+      </c>
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>36.799999999999997</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -11262,11 +11290,11 @@
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>34.068965517241374</v>
+        <v>34.093333333333327</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.8180031145717308</v>
+        <v>0.84237093066368374</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11369,11 +11397,13 @@
       <c r="AG20" s="57">
         <v>31.1</v>
       </c>
-      <c r="AH20" s="57"/>
+      <c r="AH20" s="57">
+        <v>31.3</v>
+      </c>
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -11391,11 +11421,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.210344827586212</v>
+        <v>30.24666666666667</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.5695402298850638</v>
+        <v>1.6058620689655214</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11498,11 +11528,13 @@
       <c r="AG21" s="57">
         <v>24.2</v>
       </c>
-      <c r="AH21" s="57"/>
+      <c r="AH21" s="57">
+        <v>24.9</v>
+      </c>
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11520,11 +11552,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.203448275862065</v>
+        <v>24.226666666666663</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.5939451242120946</v>
+        <v>1.6171635150166921</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11695,11 +11727,13 @@
       <c r="AG23" s="57">
         <v>30.5</v>
       </c>
-      <c r="AH23" s="57"/>
+      <c r="AH23" s="57">
+        <v>30.6</v>
+      </c>
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11717,11 +11751,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.651724137931037</v>
+        <v>28.716666666666672</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.7833370411568374</v>
+        <v>1.8482795698924726</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11824,11 +11858,13 @@
       <c r="AG24" s="57">
         <v>31</v>
       </c>
-      <c r="AH24" s="57"/>
+      <c r="AH24" s="57">
+        <v>31.5</v>
+      </c>
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11846,11 +11882,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.555172413793105</v>
+        <v>29.62</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.3033482970496237</v>
+        <v>1.3681758832565194</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11953,33 +11989,35 @@
       <c r="AG25" s="57">
         <v>32.1</v>
       </c>
-      <c r="AH25" s="57"/>
+      <c r="AH25" s="57">
+        <v>35.799999999999997</v>
+      </c>
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>32.1</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
-        <v>34.6</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AL25" s="22">
         <v>35.4</v>
       </c>
       <c r="AM25" s="23">
         <f t="shared" si="2"/>
-        <v>-0.79999999999999716</v>
+        <v>0.39999999999999858</v>
       </c>
       <c r="AN25" s="23">
         <v>30.375865393221069</v>
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.493103448275868</v>
+        <v>32.603333333333339</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>2.1172380550547985</v>
+        <v>2.2274679401122697</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12082,11 +12120,13 @@
       <c r="AG26" s="57">
         <v>19.8</v>
       </c>
-      <c r="AH26" s="57"/>
+      <c r="AH26" s="57">
+        <v>20.2</v>
+      </c>
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -12104,11 +12144,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.733793103448278</v>
+        <v>19.749333333333336</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.1909214960049184</v>
+        <v>1.2064617258899766</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12209,11 +12249,13 @@
       <c r="AG27" s="57">
         <v>22.2</v>
       </c>
-      <c r="AH27" s="57"/>
+      <c r="AH27" s="57">
+        <v>20.6</v>
+      </c>
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>22.2</v>
+        <v>20.6</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -12231,11 +12273,11 @@
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>19.142857142857142</v>
+        <v>19.193103448275863</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>2.4608065987487535</v>
+        <v>2.5110529041674745</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12338,11 +12380,13 @@
       <c r="AG28" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="AH28" s="57"/>
+      <c r="AH28" s="57">
+        <v>33.299999999999997</v>
+      </c>
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -12360,11 +12404,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>31.972413793103453</v>
+        <v>32.016666666666673</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.4439611914472934</v>
+        <v>1.4882140650105136</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12533,11 +12577,13 @@
       <c r="AG30" s="57">
         <v>36.200000000000003</v>
       </c>
-      <c r="AH30" s="57"/>
+      <c r="AH30" s="57">
+        <v>35.6</v>
+      </c>
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>36.200000000000003</v>
+        <v>35.6</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12555,11 +12601,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>35.010344827586209</v>
+        <v>35.03</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>1.2680939315288597</v>
+        <v>1.2877491039426516</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12662,11 +12708,13 @@
       <c r="AG31" s="57">
         <v>28.2</v>
       </c>
-      <c r="AH31" s="57"/>
+      <c r="AH31" s="57">
+        <v>27.6</v>
+      </c>
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -12684,11 +12732,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.310344827586206</v>
+        <v>27.32</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>1.9229199904655871</v>
+        <v>1.932575162879381</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12791,11 +12839,13 @@
       <c r="AG32" s="57">
         <v>18</v>
       </c>
-      <c r="AH32" s="57"/>
+      <c r="AH32" s="57">
+        <v>17.399999999999999</v>
+      </c>
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12813,11 +12863,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>17.8</v>
+        <v>17.786666666666669</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.4704622267387499</v>
+        <v>1.4571288934054181</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12920,11 +12970,13 @@
       <c r="AG33" s="57">
         <v>15.3</v>
       </c>
-      <c r="AH33" s="57"/>
+      <c r="AH33" s="57">
+        <v>15.6</v>
+      </c>
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12942,11 +12994,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.613793103448277</v>
+        <v>15.613333333333335</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>0.86918057100482748</v>
+        <v>0.86872080088988568</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -13101,11 +13153,13 @@
       <c r="AG35" s="57">
         <v>34.200000000000003</v>
       </c>
-      <c r="AH35" s="57"/>
+      <c r="AH35" s="57">
+        <v>32.799999999999997</v>
+      </c>
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>34.200000000000003</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -13123,11 +13177,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>31.993103448275861</v>
+        <v>32.019999999999996</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.92040759574129893</v>
+        <v>0.94730414746543445</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -13351,11 +13405,13 @@
       <c r="AG38" s="57">
         <v>30.7</v>
       </c>
-      <c r="AH38" s="57"/>
+      <c r="AH38" s="57">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>30.7</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -13373,11 +13429,11 @@
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>0.17097377660741842</v>
+        <v>0.27097377660741984</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -13481,11 +13537,13 @@
       <c r="AG39" s="57">
         <v>33.6</v>
       </c>
-      <c r="AH39" s="57"/>
+      <c r="AH39" s="57">
+        <v>34.4</v>
+      </c>
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -13503,11 +13561,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.603448275862068</v>
+        <v>31.696666666666665</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.760315164998147</v>
+        <v>0.85353355580274481</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13611,11 +13669,13 @@
       <c r="AG40" s="57">
         <v>28.8</v>
       </c>
-      <c r="AH40" s="57"/>
+      <c r="AH40" s="57">
+        <v>31.8</v>
+      </c>
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>28.8</v>
+        <v>31.8</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13633,11 +13693,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>30.00344827586207</v>
+        <v>30.063333333333333</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>1.0558998887652891</v>
+        <v>1.1157849462365519</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13741,11 +13801,13 @@
       <c r="AG41" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="AH41" s="57"/>
+      <c r="AH41" s="57">
+        <v>32.200000000000003</v>
+      </c>
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13763,11 +13825,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.800000000000008</v>
+        <v>30.846666666666678</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>1.4336917562724167</v>
+        <v>1.4803584229390871</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13932,7 +13994,9 @@
       <c r="AG43" s="57">
         <v>33.4</v>
       </c>
-      <c r="AH43" s="57"/>
+      <c r="AH43" s="57">
+        <v>33.4</v>
+      </c>
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
@@ -13954,11 +14018,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>31.415384615384614</v>
+        <v>31.488888888888887</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>1.3543227874276234</v>
+        <v>1.4278270609318966</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -14060,11 +14124,13 @@
       <c r="AG44" s="57">
         <v>32</v>
       </c>
-      <c r="AH44" s="57"/>
+      <c r="AH44" s="57">
+        <v>30.4</v>
+      </c>
       <c r="AI44" s="57"/>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>30.4</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -14082,11 +14148,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.314285714285713</v>
+        <v>31.282758620689652</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.2710985089252524</v>
+        <v>2.2395714153291912</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -14190,11 +14256,13 @@
       <c r="AG45" s="57">
         <v>33</v>
       </c>
-      <c r="AH45" s="57"/>
+      <c r="AH45" s="57">
+        <v>28.8</v>
+      </c>
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>28.8</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -14212,11 +14280,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.813793103448283</v>
+        <v>30.746666666666673</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>1.267976710569453</v>
+        <v>1.200850273787843</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -14459,11 +14527,13 @@
       <c r="AG48" s="57">
         <v>32.4</v>
       </c>
-      <c r="AH48" s="57"/>
+      <c r="AH48" s="57">
+        <v>31.5</v>
+      </c>
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>31.5</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -14481,11 +14551,11 @@
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.81379310344828</v>
+        <v>30.83666666666667</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.47126024801220012</v>
+        <v>0.49413381123058997</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27384,6 +27454,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -27393,12 +27469,6 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
